--- a/out/MLP_Base_repeat_1_000006.xlsx
+++ b/out/MLP_Base_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6077945103300888</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.45907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6077945103300888</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003822755919395713</v>
+        <v>-0.0003128222096160753</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4920184646617904</v>
+        <v>0.4026263409910837</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9849680649333461</v>
+        <v>0.806015066578293</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1136272870386607</v>
+        <v>-0.09298306858678258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3780089020311903</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3780089020311903</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3775855311457901</v>
+        <v>0.3089949417553572</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.300686759814212</v>
+        <v>1.030754323529692</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.98154934730433</v>
+        <v>2.372556386773466</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2488718178992786</v>
+        <v>0.1972232256246942</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.45907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.176707800499683</v>
+        <v>1.734744129634345</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4359225915783179</v>
+        <v>0.3454551839555684</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.799803160808304</v>
+        <v>2.228528260576171</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.238727074631071</v>
+        <v>0.1891838300539991</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.840958979557389</v>
+        <v>2.26114301674595</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09859775847362359</v>
+        <v>0.07813567695078479</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.799177161483286</v>
+        <v>2.22803213394136</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1228443459685831</v>
+        <v>0.09735034832865293</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.94628464413913</v>
+        <v>2.34461085647105</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07396816436794665</v>
+        <v>0.05861748466870621</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.971293264834567</v>
+        <v>2.36442961625947</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05623568965199581</v>
+        <v>0.0445650463841772</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.009764872269103</v>
+        <v>2.394917792165746</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02487239749046113</v>
+        <v>0.01971203038416808</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.003225968819732</v>
+        <v>2.389735703386273</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01973769542071214</v>
+        <v>0.01564027987761302</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.017818415129895</v>
+        <v>2.401299760912972</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009785793750575953</v>
+        <v>0.007754591776772256</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.017638673761089</v>
+        <v>2.401156271458186</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005688305859197012</v>
+        <v>0.004507170356471418</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.019224320461084</v>
+        <v>2.402411921959817</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002840198329225691</v>
+        <v>0.002249630577862894</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.019215777997098</v>
+        <v>2.402404114792548</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001400702951404652</v>
+        <v>0.001110363487004101</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.019175159444777</v>
+        <v>2.402370880486227</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008127249305861704</v>
+        <v>0.0006425046389131309</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.019396290736876</v>
+        <v>2.402544939550174</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002673003539045728</v>
+        <v>0.000211501101055275</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.019119730386179</v>
+        <v>2.40232490697687</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001319932599835336</v>
+        <v>0.0001027979750690101</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.019116260084407</v>
+        <v>2.402321113622841</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.08320800333637e-05</v>
+        <v>5.370870712260415e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.019123605079162</v>
+        <v>2.402325871683893</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.055270670444892e-05</v>
+        <v>2.344216536355913e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.85907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.019116201143556</v>
+        <v>2.402318933314006</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.019119806852748</v>
+        <v>2.4023209272638</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.45907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.019112137131653</v>
+        <v>2.402313592869656</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.45907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.019108651911345</v>
+        <v>2.402310107649348</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.01910410459916</v>
+        <v>2.402305560337163</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.01910419454381</v>
+        <v>2.402305650281813</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.019103336610225</v>
+        <v>2.402304792348227</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.01910356493126</v>
+        <v>2.402305020669262</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.45907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.019102769267048</v>
+        <v>2.402304225005051</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.019102831536421</v>
+        <v>2.402304287274423</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.019102859211698</v>
+        <v>2.402304314949701</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.019103011425721</v>
+        <v>2.402304467163723</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.019102665484759</v>
+        <v>2.402304121222762</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6077945103300888</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.019102741591771</v>
+        <v>2.402304197329773</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.019102907643433</v>
+        <v>2.402304363381435</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.019103267422032</v>
+        <v>2.402304723160035</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.45907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.01910328817849</v>
+        <v>2.402304743916493</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.019103391960779</v>
+        <v>2.402304847698781</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6077945103300888</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.019103620281814</v>
+        <v>2.402305076019816</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.019103495743067</v>
+        <v>2.40230495148107</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.019103523418345</v>
+        <v>2.402304979156347</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.85907883537967</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.019103578768898</v>
+        <v>2.402305034506901</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.019103841684029</v>
+        <v>2.402305297422032</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.019103758658198</v>
+        <v>2.4023052143962</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.019103551093621</v>
+        <v>2.402305006831623</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.01910356493126</v>
+        <v>2.402305020669262</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.019103703307644</v>
+        <v>2.402305159045647</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.019103419636056</v>
+        <v>2.402304875374058</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.019103246665575</v>
+        <v>2.402304702403578</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.019103142883287</v>
+        <v>2.402304598621289</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.01910328817849</v>
+        <v>2.402304743916493</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.019103530337164</v>
+        <v>2.402304986075166</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.019103357366683</v>
+        <v>2.402304813104685</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.019103059857456</v>
+        <v>2.402304515595458</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.019103046019817</v>
+        <v>2.40230450175782</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.019102679322398</v>
+        <v>2.4023041350604</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.019102679322398</v>
+        <v>2.4023041350604</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.019102617053025</v>
+        <v>2.402304072791027</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.019102513270736</v>
+        <v>2.402303969008738</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.019102340300255</v>
+        <v>2.402303796038258</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.01910238873199</v>
+        <v>2.402303844469992</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.01910202895339</v>
+        <v>2.402303484691393</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.019101987440475</v>
+        <v>2.402303443178477</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.019102042791029</v>
+        <v>2.402303498529031</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.019102098141583</v>
+        <v>2.402303553879585</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.019102139654498</v>
+        <v>2.4023035953925</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.019101869820548</v>
+        <v>2.40230332555855</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.019101925171102</v>
+        <v>2.402303380909104</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.019102070466305</v>
+        <v>2.402303526204308</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.019102035872209</v>
+        <v>2.402303491610212</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.019102022034571</v>
+        <v>2.402303477772573</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.207794510330089</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.019102111979221</v>
+        <v>2.402303567717223</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.45907883537967</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.019102430244905</v>
+        <v>2.402303885982908</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.019102250355605</v>
+        <v>2.402303706093608</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.019102291868521</v>
+        <v>2.402303747606523</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.019102105060402</v>
+        <v>2.402303560798404</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.019102174248594</v>
+        <v>2.402303629986596</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.019101973602837</v>
+        <v>2.402303429340839</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.019102015115752</v>
+        <v>2.402303470853755</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.019102042791029</v>
+        <v>2.402303498529031</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_1_000006.xlsx
+++ b/out/MLP_Base_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.45907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003822755919395713</v>
+        <v>-0.0002883129447629908</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4920184646617904</v>
+        <v>0.3710810079453581</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9849680649333461</v>
+        <v>0.742864701542533</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1136272870386607</v>
+        <v>-0.08569795457143624</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3780089020311903</v>
+        <v>0.285094740429159</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3780089020311903</v>
+        <v>0.285094740429159</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3775855311457901</v>
+        <v>0.2847885657230497</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.300686759814212</v>
+        <v>0.9406349133637311</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.98154934730433</v>
+        <v>2.167931416415669</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2488718178992786</v>
+        <v>0.1799798298269965</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.176707800499683</v>
+        <v>1.585883614501448</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4359225915783179</v>
+        <v>0.3152519584218518</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.85907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.799803160808304</v>
+        <v>2.036495802114054</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.238727074631071</v>
+        <v>0.1726432063763796</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.85907883537967</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.840958979557389</v>
+        <v>2.066259005266124</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09859775847362359</v>
+        <v>0.07130435529741322</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.85907883537967</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.799177161483286</v>
+        <v>2.036043048564383</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1228443459685831</v>
+        <v>0.0888386173529945</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.85907883537967</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.94628464413913</v>
+        <v>2.142428877745989</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07396816436794665</v>
+        <v>0.0534923231409281</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.85907883537967</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.971293264834567</v>
+        <v>2.160514821508132</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05623568965199581</v>
+        <v>0.04066944385295242</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266862</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.009764872269103</v>
+        <v>2.188337346459352</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02487239749046113</v>
+        <v>0.01798820085512622</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.003225968819732</v>
+        <v>2.18360843462239</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01973769542071214</v>
+        <v>0.01427324107482948</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.017818415129895</v>
+        <v>2.194160769307998</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009785793750575953</v>
+        <v>0.007074189145153282</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.017638673761089</v>
+        <v>2.194029402595047</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005688305859197012</v>
+        <v>0.0041115190550658</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.85907883537967</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.019224320461084</v>
+        <v>2.195174920708546</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002840198329225691</v>
+        <v>0.002054714127905715</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.019215777997098</v>
+        <v>2.195167356225415</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001400702951404652</v>
+        <v>0.001012625449483123</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.019175159444777</v>
+        <v>2.195136596059338</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008127249305861704</v>
+        <v>0.0005857645416887843</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.019396290736876</v>
+        <v>2.195294964380569</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002673003539045728</v>
+        <v>0.0001914133700295279</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.019119730386179</v>
+        <v>2.195093776272061</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001319932599835336</v>
+        <v>9.38148104799259e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.019116260084407</v>
+        <v>2.195089883517337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.08320800333637e-05</v>
+        <v>4.881631486238714e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.019123605079162</v>
+        <v>2.195093845127114</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.055270670444892e-05</v>
+        <v>2.107198491659588e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.019116201143556</v>
+        <v>2.1950870619458</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.85907883537967</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.019119806852748</v>
+        <v>2.195088516227694</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.45907883537967</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.019112137131653</v>
+        <v>2.195081513936873</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.019108651911345</v>
+        <v>2.195077651861777</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.01910410459916</v>
+        <v>2.195073104549592</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.01910419454381</v>
+        <v>2.195073194494242</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.019103336610225</v>
+        <v>2.195072336560657</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.01910356493126</v>
+        <v>2.195072564881692</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.45907883537967</v>
+        <v>0.7395115795266862</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.019102769267048</v>
+        <v>2.19507176921748</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.019102831536421</v>
+        <v>2.195071831486853</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.019102859211698</v>
+        <v>2.19507185916213</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.85907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.019103011425721</v>
+        <v>2.195072011376153</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.019102665484759</v>
+        <v>2.195071665435191</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.019102741591771</v>
+        <v>2.195071741542203</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.019102907643433</v>
+        <v>2.195071907593865</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.019103267422032</v>
+        <v>2.195072267372464</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.01910328817849</v>
+        <v>2.195072288128922</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.019103391960779</v>
+        <v>2.19507239191121</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.019103620281814</v>
+        <v>2.195072620232245</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.019103495743067</v>
+        <v>2.195072495693499</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.019103523418345</v>
+        <v>2.195072523368776</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.85907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.019103578768898</v>
+        <v>2.19507257871933</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.019103841684029</v>
+        <v>2.195072841634461</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.019103758658198</v>
+        <v>2.19507275860863</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.019103551093621</v>
+        <v>2.195072551044053</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.01910356493126</v>
+        <v>2.195072564881692</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.019103703307644</v>
+        <v>2.195072703258076</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.019103419636056</v>
+        <v>2.195072419586487</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.019103246665575</v>
+        <v>2.195072246616007</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.019103142883287</v>
+        <v>2.195072142833719</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.01910328817849</v>
+        <v>2.195072288128922</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.019103530337164</v>
+        <v>2.195072530287595</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.019103357366683</v>
+        <v>2.195072357317115</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.019103059857456</v>
+        <v>2.195072059807888</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.019103046019817</v>
+        <v>2.195072045970249</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.019102679322398</v>
+        <v>2.19507167927283</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.019102679322398</v>
+        <v>2.19507167927283</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.019102617053025</v>
+        <v>2.195071617003457</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.019102513270736</v>
+        <v>2.195071513221168</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.019102340300255</v>
+        <v>2.195071340250687</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.01910238873199</v>
+        <v>2.195071388682422</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.01910202895339</v>
+        <v>2.195071028903822</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.019101987440475</v>
+        <v>2.195070987390907</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.019102042791029</v>
+        <v>2.19507104274146</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.019102098141583</v>
+        <v>2.195071098092015</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.019102139654498</v>
+        <v>2.19507113960493</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.019101869820548</v>
+        <v>2.19507086977098</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.019101925171102</v>
+        <v>2.195070925121533</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.019102070466305</v>
+        <v>2.195071070416737</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.019102035872209</v>
+        <v>2.195071035822641</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.019102022034571</v>
+        <v>2.195071021985003</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.019102111979221</v>
+        <v>2.195071111929653</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.45907883537967</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.019102430244905</v>
+        <v>2.195071430195337</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.019102250355605</v>
+        <v>2.195071250306037</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.019102291868521</v>
+        <v>2.195071291818953</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.019102105060402</v>
+        <v>2.195071105010834</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.019102174248594</v>
+        <v>2.195071174199025</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.019101973602837</v>
+        <v>2.195070973553268</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.019102015115752</v>
+        <v>2.195071015066184</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.019102042791029</v>
+        <v>2.19507104274146</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_1_000006.xlsx
+++ b/out/MLP_Base_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4182939231395721</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4203661680221558</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9299999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4381938576698303</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4661273062229156</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4193671047687531</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4462050795555115</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3929381966590881</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4555021524429321</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4607627689838409</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4189417362213135</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3946996331214905</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3722766935825348</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4261200726032257</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.383214145898819</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3745808303356171</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3705814778804779</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.402918815612793</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4283149242401123</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4715571403503418</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4223228991031647</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4057371020317078</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3791062235832214</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3857735693454742</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4526892006397247</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3943082988262177</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4824291169643402</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5708032846450806</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5102058053016663</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9395115795266863</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4569108784198761</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4630813896656036</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4624876642263467</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4098028242588043</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3839319944381714</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4107532501220703</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5238796472549438</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4654017686843872</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4573048055171967</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4900586307048798</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4343866407871246</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4540838897228241</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4927746951580048</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.03851195765016982</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5436340570449829</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.562671959400177</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.640511201403203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.611879289150238</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.640511201403203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002883129447629908</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3710810079453581</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5911092162132263</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.640511201403203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.742864701542533</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08569795457143624</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5170451402664185</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.640511201403203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.285094740429159</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5620667338371277</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.640511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.285094740429159</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5564616322517395</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.640511201403203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2847885657230497</v>
+        <v>0.2122727167830646</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.9406349133637311</v>
+        <v>0.3661950314083699</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5089004635810852</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.640511201403203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.167931416415669</v>
+        <v>0.9453922846818488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1799798298269965</v>
+        <v>0.07006735519795214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5766862034797668</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.640511201403203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.585883614501448</v>
+        <v>0.718797248674785</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3152519584218518</v>
+        <v>0.1227294001466499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5533816814422607</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.640511201403203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.036495802114054</v>
+        <v>0.8942234757282896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1726432063763796</v>
+        <v>0.06721132397827324</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5631313323974609</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.440511201403203</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.066259005266124</v>
+        <v>0.9058105027624485</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07130435529741322</v>
+        <v>0.02775905880951137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5358681678771973</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.440511201403203</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.036043048564383</v>
+        <v>0.8940472319822265</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0888386173529945</v>
+        <v>0.03458540515472364</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6215510368347168</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.440511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.142428877745989</v>
+        <v>0.935464230815531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0534923231409281</v>
+        <v>0.02082547197424655</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5308288931846619</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.440511201403203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.160514821508132</v>
+        <v>0.9425053184761174</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04066944385295242</v>
+        <v>0.01583205915755942</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6569768786430359</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7395115795266862</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.188337346459352</v>
+        <v>0.9533368633026545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01798820085512622</v>
+        <v>0.007000599424997798</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4428487420082092</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.18360843462239</v>
+        <v>0.951492997726175</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01427324107482948</v>
+        <v>0.005553954836411267</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3315777182579041</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.194160769307998</v>
+        <v>0.9555982901916548</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.007074189145153282</v>
+        <v>0.002751631250162162</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7326245903968811</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7395115795266863</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.194029402595047</v>
+        <v>0.9555440911654862</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0041115190550658</v>
+        <v>0.001597969610841877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7210431098937988</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.440511201403203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.195174920708546</v>
+        <v>0.9559869431489801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002054714127905715</v>
+        <v>0.0007950302050481237</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5944038033485413</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.640511201403203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.195167356225415</v>
+        <v>0.9559809470573687</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001012625449483123</v>
+        <v>0.0003917014464086749</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5907249450683594</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.640511201403203</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.195136596059338</v>
+        <v>0.9559659049587285</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005857645416887843</v>
+        <v>0.0002252980416752888</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.6075936555862427</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.640511201403203</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.195294964380569</v>
+        <v>0.9560245909144622</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001914133700295279</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.5287163257598877</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.640511201403203</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.195093776272061</v>
+        <v>0.9559431116611959</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>9.38148104799259e-05</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5353103280067444</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9395115795266863</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.195089883517337</v>
+        <v>0.9559385479517856</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.881631486238714e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4906134009361267</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9395115795266864</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.195093845127114</v>
+        <v>0.9559371319825209</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.107198491659588e-05</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5354041457176208</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7395115795266863</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.1950870619458</v>
+        <v>0.9559314351212175</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.5532674789428711</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.440511201403203</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.195088516227694</v>
+        <v>0.9559291262164156</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.533724308013916</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.440511201403203</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.195081513936873</v>
+        <v>0.9559231266828189</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.5646234750747681</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9395115795266863</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.195077651861777</v>
+        <v>0.9559188840726649</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4728789627552032</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.195073104549592</v>
+        <v>0.9559191123936995</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4949250817298889</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.195073194494242</v>
+        <v>0.9559192023383496</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4834807813167572</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.195072336560657</v>
+        <v>0.9559183444047648</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.5181415677070618</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7395115795266863</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.195072564881692</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5346859097480774</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7395115795266862</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.19507176921748</v>
+        <v>0.9559177770615876</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4547587037086487</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.195071831486853</v>
+        <v>0.9559178393309608</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4711885154247284</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.19507185916213</v>
+        <v>0.9559178670062376</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5124896168708801</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.195072011376153</v>
+        <v>0.9559180192202609</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4528563618659973</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.195071665435191</v>
+        <v>0.9559176732792992</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4697432219982147</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.195071741542203</v>
+        <v>0.9559177493863108</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4087597727775574</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.195071907593865</v>
+        <v>0.9559179154379724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.5071331262588501</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7395115795266863</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.195072267372464</v>
+        <v>0.9559182752165725</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5287634134292603</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.640511201403203</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.195072288128922</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5561526417732239</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9395115795266863</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.19507239191121</v>
+        <v>0.9559183997553187</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4615389108657837</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.195072620232245</v>
+        <v>0.9559186280763533</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4270673096179962</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.195072495693499</v>
+        <v>0.9559185035376071</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3841065168380737</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.195072523368776</v>
+        <v>0.9559185312128839</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.5005219578742981</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.19507257871933</v>
+        <v>0.955918586563438</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.4289514124393463</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.195072841634461</v>
+        <v>0.9559188494785686</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4363775551319122</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.19507275860863</v>
+        <v>0.9559187664527379</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4098534286022186</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.195072551044053</v>
+        <v>0.9559185588881611</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3994411528110504</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.195072564881692</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3913571834564209</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.195072703258076</v>
+        <v>0.9559187111021842</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3897115886211395</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.195072419586487</v>
+        <v>0.9559184274305955</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3731124997138977</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.195072246616007</v>
+        <v>0.9559182544601148</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4512384831905365</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.195072142833719</v>
+        <v>0.9559181506778263</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.406827837228775</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.195072288128922</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3739118874073029</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.195072530287595</v>
+        <v>0.9559185381317034</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3881989419460297</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.195072357317115</v>
+        <v>0.9559183651612224</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3693048655986786</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.195072059807888</v>
+        <v>0.9559180676519955</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4000390768051147</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.195072045970249</v>
+        <v>0.9559180538143569</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3845910429954529</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.19507167927283</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4140631556510925</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.19507167927283</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4764488041400909</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.195071617003457</v>
+        <v>0.9559176248475646</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3934145569801331</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.195071513221168</v>
+        <v>0.9559175210652762</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4041029512882233</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.195071340250687</v>
+        <v>0.9559173480947953</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4193144142627716</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.195071388682422</v>
+        <v>0.95591739652653</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.408265084028244</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.195071028903822</v>
+        <v>0.9559170367479298</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3917292058467865</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.195070987390907</v>
+        <v>0.9559169952350145</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4336058497428894</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.19507104274146</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3733855783939362</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.195071098092015</v>
+        <v>0.9559171059361221</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3822143077850342</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.19507113960493</v>
+        <v>0.9559171474490376</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3834551870822906</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.19507086977098</v>
+        <v>0.9559168776150875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3905915021896362</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.195070925121533</v>
+        <v>0.9559169329656414</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3767614364624023</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.195071070416737</v>
+        <v>0.9559170782608453</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.381902664899826</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.195071035822641</v>
+        <v>0.955917043666749</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3706610500812531</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.195071021985003</v>
+        <v>0.9559170298291105</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4622534215450287</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.195071111929653</v>
+        <v>0.9559171197737607</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5539243221282959</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.195071430195337</v>
+        <v>0.9559174380394453</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4622805714607239</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.195071250306037</v>
+        <v>0.9559172581501452</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4451831877231598</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4624876642263467</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.195071291818953</v>
+        <v>0.9559172996630606</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4439768493175507</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4624876642263467</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.195071105010834</v>
+        <v>0.9559171128549413</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3987248539924622</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.195071174199025</v>
+        <v>0.9559171820431338</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4307571649551392</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.195070973553268</v>
+        <v>0.9559169813973759</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3957446813583374</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.195071015066184</v>
+        <v>0.9559170229102913</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4246173501014709</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7200000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.19507104274146</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
   </sheetData>
